--- a/sitepreview/pcmt/v0.1.0/StructureDefinition-ProductAuthorization.xlsx
+++ b/sitepreview/pcmt/v0.1.0/StructureDefinition-ProductAuthorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T12:59:37+00:00</t>
+    <t>2025-06-26T06:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
